--- a/projects/skill_modify_excel_with_r/statistischer_bericht_demo.xlsx
+++ b/projects/skill_modify_excel_with_r/statistischer_bericht_demo.xlsx
@@ -43,7 +43,7 @@
     <numFmt numFmtId="177" formatCode="0,00"/>
     <numFmt numFmtId="178" formatCode="0,00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,25 +54,26 @@
     <font>
       <b val="1"/>
       <color rgb="FF004B76"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <sz val="14"/>
     </font>
     <font>
+      <b val="0"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <sz val="12"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="FF004B76"/>
-      <name val="Aptos Narrow"/>
-      <sz val="14"/>
+      <b val="0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <color theme="10"/>
@@ -82,31 +83,41 @@
     </font>
     <font>
       <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF004B76"/>
+      <name val="Arial"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <sz val="16"/>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF004B76"/>
-      <name val="Aptos Narrow"/>
-      <sz val="12"/>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -140,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
@@ -149,28 +160,43 @@
     <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="165" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="168" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="166" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="167" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="169" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="171" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="173" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="175" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="177" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="178" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -521,16 +547,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EVAS-Nummer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>61241</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>EVAS-Nummer: 61241</t>
         </is>
       </c>
     </row>
@@ -545,242 +564,237 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>61241-02: Preise für ausgewählte Mineralölerzeugnisse</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monat und Jahr</t>
-        </is>
-      </c>
+      <c r="B3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Monat_Jahr</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Motorenbenzin_E5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Januar 2020</t>
         </is>
       </c>
-      <c r="B5" s="22">
-        <v>97.148569393903</v>
+      <c r="B5" s="34">
+        <v>135.865793242119</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Februar 2020</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <v>99.1600748477504</v>
+      <c r="B6" s="34">
+        <v>138.344800015911</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>März 2020</t>
         </is>
       </c>
-      <c r="B7" s="22">
-        <v>131.472318237647</v>
+      <c r="B7" s="34">
+        <v>133.20068910718</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>April 2020</t>
         </is>
       </c>
-      <c r="B8" s="22">
-        <v>139.456354132853</v>
+      <c r="B8" s="34">
+        <v>135.121662043966</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Januar 2021</t>
         </is>
       </c>
-      <c r="B9" s="22">
-        <v>83.784555150196</v>
+      <c r="B9" s="34">
+        <v>89.1757570626214</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Februar 2021</t>
         </is>
       </c>
-      <c r="B10" s="22">
-        <v>115.273719606921</v>
+      <c r="B10" s="34">
+        <v>126.497217006981</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>März 2021</t>
         </is>
       </c>
-      <c r="B11" s="22">
-        <v>129.957496635616</v>
+      <c r="B11" s="34">
+        <v>102.724851034582</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>April 2021</t>
         </is>
       </c>
-      <c r="B12" s="22">
-        <v>124.463326702826</v>
+      <c r="B12" s="34">
+        <v>98.9447790849954</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Januar 2022</t>
         </is>
       </c>
-      <c r="B13" s="22">
-        <v>84.1207860317081</v>
+      <c r="B13" s="34">
+        <v>113.418734893203</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Februar 2022</t>
         </is>
       </c>
-      <c r="B14" s="22">
-        <v>102.540241908282</v>
+      <c r="B14" s="34">
+        <v>124.949937295169</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>März 2022</t>
         </is>
       </c>
-      <c r="B15" s="22">
-        <v>136.709443642758</v>
+      <c r="B15" s="34">
+        <v>103.58089662157</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>April 2022</t>
         </is>
       </c>
-      <c r="B16" s="22">
-        <v>95.3690006164834</v>
+      <c r="B16" s="34">
+        <v>134.48971261736</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Januar 2023</t>
         </is>
       </c>
-      <c r="B17" s="22">
-        <v>122.046595248394</v>
+      <c r="B17" s="34">
+        <v>123.35365481209</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Februar 2023</t>
         </is>
       </c>
-      <c r="B18" s="22">
-        <v>120.705243223347</v>
+      <c r="B18" s="34">
+        <v>91.7267335392535</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>März 2023</t>
         </is>
       </c>
-      <c r="B19" s="22">
-        <v>96.4445403916761</v>
+      <c r="B19" s="34">
+        <v>135.919500230812</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>April 2023</t>
         </is>
       </c>
-      <c r="B20" s="22">
-        <v>115.550537155941</v>
+      <c r="B20" s="34">
+        <v>103.738525854424</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Januar 2024</t>
         </is>
       </c>
-      <c r="B21" s="22">
-        <v>136.526093548164</v>
+      <c r="B21" s="34">
+        <v>83.6907474184409</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Februar 2024</t>
         </is>
       </c>
-      <c r="B22" s="22">
-        <v>111.659262664616</v>
+      <c r="B22" s="34">
+        <v>85.6497246865183</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>März 2024</t>
         </is>
       </c>
-      <c r="B23" s="22">
-        <v>99.0189150208607</v>
+      <c r="B23" s="34">
+        <v>99.7990381531417</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>April 2024</t>
         </is>
       </c>
-      <c r="B24" s="22">
-        <v>119.43249699194</v>
+      <c r="B24" s="34">
+        <v>136.984818275087</v>
       </c>
     </row>
   </sheetData>
@@ -799,229 +813,235 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>61241-02-b: Tabelle mit 20 Zeilen und 2 Spalten für barrierefreien Zugang.</t>
-        </is>
-      </c>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Tabelle 61241-02. Sie erstreckt sich über 2 Spalten und 20 Zeilen.</t>
+        </is>
+      </c>
+      <c r="B1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Monat_Jahr</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Motorenbenzin_E5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Januar 2020</t>
         </is>
       </c>
-      <c r="B5" s="23">
-        <v>97.148569393903</v>
+      <c r="B5" s="36">
+        <v>135.865793242119</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Februar 2020</t>
         </is>
       </c>
-      <c r="B6" s="23">
-        <v>99.1600748477504</v>
+      <c r="B6" s="36">
+        <v>138.344800015911</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>März 2020</t>
         </is>
       </c>
-      <c r="B7" s="23">
-        <v>131.472318237647</v>
+      <c r="B7" s="36">
+        <v>133.20068910718</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>April 2020</t>
         </is>
       </c>
-      <c r="B8" s="23">
-        <v>139.456354132853</v>
+      <c r="B8" s="36">
+        <v>135.121662043966</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Januar 2021</t>
         </is>
       </c>
-      <c r="B9" s="23">
-        <v>83.784555150196</v>
+      <c r="B9" s="36">
+        <v>89.1757570626214</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Februar 2021</t>
         </is>
       </c>
-      <c r="B10" s="23">
-        <v>115.273719606921</v>
+      <c r="B10" s="36">
+        <v>126.497217006981</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>März 2021</t>
         </is>
       </c>
-      <c r="B11" s="23">
-        <v>129.957496635616</v>
+      <c r="B11" s="36">
+        <v>102.724851034582</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>April 2021</t>
         </is>
       </c>
-      <c r="B12" s="23">
-        <v>124.463326702826</v>
+      <c r="B12" s="36">
+        <v>98.9447790849954</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Januar 2022</t>
         </is>
       </c>
-      <c r="B13" s="23">
-        <v>84.1207860317081</v>
+      <c r="B13" s="36">
+        <v>113.418734893203</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Februar 2022</t>
         </is>
       </c>
-      <c r="B14" s="23">
-        <v>102.540241908282</v>
+      <c r="B14" s="36">
+        <v>124.949937295169</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>März 2022</t>
         </is>
       </c>
-      <c r="B15" s="23">
-        <v>136.709443642758</v>
+      <c r="B15" s="36">
+        <v>103.58089662157</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>April 2022</t>
         </is>
       </c>
-      <c r="B16" s="23">
-        <v>95.3690006164834</v>
+      <c r="B16" s="36">
+        <v>134.48971261736</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Januar 2023</t>
         </is>
       </c>
-      <c r="B17" s="23">
-        <v>122.046595248394</v>
+      <c r="B17" s="36">
+        <v>123.35365481209</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Februar 2023</t>
         </is>
       </c>
-      <c r="B18" s="23">
-        <v>120.705243223347</v>
+      <c r="B18" s="36">
+        <v>91.7267335392535</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>März 2023</t>
         </is>
       </c>
-      <c r="B19" s="23">
-        <v>96.4445403916761</v>
+      <c r="B19" s="36">
+        <v>135.919500230812</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>April 2023</t>
         </is>
       </c>
-      <c r="B20" s="23">
-        <v>115.550537155941</v>
+      <c r="B20" s="36">
+        <v>103.738525854424</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Januar 2024</t>
         </is>
       </c>
-      <c r="B21" s="23">
-        <v>136.526093548164</v>
+      <c r="B21" s="36">
+        <v>83.6907474184409</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Februar 2024</t>
         </is>
       </c>
-      <c r="B22" s="23">
-        <v>111.659262664616</v>
+      <c r="B22" s="36">
+        <v>85.6497246865183</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>März 2024</t>
         </is>
       </c>
-      <c r="B23" s="23">
-        <v>99.0189150208607</v>
+      <c r="B23" s="36">
+        <v>99.7990381531417</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>April 2024</t>
         </is>
       </c>
-      <c r="B24" s="23">
-        <v>119.43249699194</v>
+      <c r="B24" s="36">
+        <v>136.984818275087</v>
       </c>
     </row>
   </sheetData>
@@ -1036,332 +1056,245 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CSV-Daten zu Tabelle 61241-02</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
+        </is>
+      </c>
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Monat_Jahr</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Motorenbenzin_E5</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Januar 2020</t>
         </is>
       </c>
-      <c r="C2">
-        <v>97.148569393903</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" s="8">
+        <v>135.865793242119</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Februar 2020</t>
         </is>
       </c>
-      <c r="C3">
-        <v>99.1600748477504</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" s="8">
+        <v>138.344800015911</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>März 2020</t>
         </is>
       </c>
-      <c r="C4">
-        <v>131.472318237647</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" s="8">
+        <v>133.20068910718</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>April 2020</t>
         </is>
       </c>
-      <c r="C5">
-        <v>139.456354132853</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" s="8">
+        <v>135.121662043966</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Januar 2021</t>
         </is>
       </c>
-      <c r="C6">
-        <v>83.784555150196</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" s="8">
+        <v>89.1757570626214</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Februar 2021</t>
         </is>
       </c>
-      <c r="C7">
-        <v>115.273719606921</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" s="8">
+        <v>126.497217006981</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>März 2021</t>
         </is>
       </c>
-      <c r="C8">
-        <v>129.957496635616</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" s="8">
+        <v>102.724851034582</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>April 2021</t>
         </is>
       </c>
-      <c r="C9">
-        <v>124.463326702826</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" s="8">
+        <v>98.9447790849954</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Januar 2022</t>
         </is>
       </c>
-      <c r="C10">
-        <v>84.1207860317081</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" s="8">
+        <v>113.418734893203</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Februar 2022</t>
         </is>
       </c>
-      <c r="C11">
-        <v>102.540241908282</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" s="8">
+        <v>124.949937295169</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>März 2022</t>
         </is>
       </c>
-      <c r="C12">
-        <v>136.709443642758</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" s="8">
+        <v>103.58089662157</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>April 2022</t>
         </is>
       </c>
-      <c r="C13">
-        <v>95.3690006164834</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" s="8">
+        <v>134.48971261736</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Januar 2023</t>
         </is>
       </c>
-      <c r="C14">
-        <v>122.046595248394</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" s="8">
+        <v>123.35365481209</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Februar 2023</t>
         </is>
       </c>
-      <c r="C15">
-        <v>120.705243223347</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" s="8">
+        <v>91.7267335392535</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>März 2023</t>
         </is>
       </c>
-      <c r="C16">
-        <v>96.4445403916761</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" s="8">
+        <v>135.919500230812</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>April 2023</t>
         </is>
       </c>
-      <c r="C17">
-        <v>115.550537155941</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" s="8">
+        <v>103.738525854424</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Januar 2024</t>
         </is>
       </c>
-      <c r="C18">
-        <v>136.526093548164</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" s="8">
+        <v>83.6907474184409</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Februar 2024</t>
         </is>
       </c>
-      <c r="C19">
-        <v>111.659262664616</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" s="8">
+        <v>85.6497246865183</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>März 2024</t>
         </is>
       </c>
-      <c r="C20">
-        <v>99.0189150208607</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" s="8">
+        <v>99.7990381531417</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>April 2024</t>
         </is>
       </c>
-      <c r="C21">
-        <v>119.43249699194</v>
+      <c r="B24" s="8">
+        <v>136.984818275087</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1372,165 +1305,162 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>61241-03: Preise für ausgewählte Mineralölerzeugnisse</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monat und Jahr</t>
-        </is>
-      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Monat_Jahr</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Dieselkraftstoff_ab_Lager</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Dieselkraftstoff_frei_Verbrauchsstelle</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Januar 2023</t>
         </is>
       </c>
-      <c r="B5" s="24">
-        <v>128.245580354705</v>
-      </c>
-      <c r="C5" s="25">
-        <v>113.84433391504</v>
+      <c r="B5" s="39">
+        <v>119.122709678486</v>
+      </c>
+      <c r="C5" s="40">
+        <v>89.2437729332596</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Februar 2023</t>
         </is>
       </c>
-      <c r="B6" s="24">
-        <v>111.428374904208</v>
-      </c>
-      <c r="C6" s="25">
-        <v>93.3277661539614</v>
+      <c r="B6" s="39">
+        <v>100.902110515162</v>
+      </c>
+      <c r="C6" s="40">
+        <v>114.396699322388</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>März 2023</t>
         </is>
       </c>
-      <c r="B7" s="24">
-        <v>128.144519217312</v>
-      </c>
-      <c r="C7" s="25">
-        <v>91.056316816248</v>
+      <c r="B7" s="39">
+        <v>99.4472182774916</v>
+      </c>
+      <c r="C7" s="40">
+        <v>77.5183631898835</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Januar 2024</t>
         </is>
       </c>
-      <c r="B8" s="24">
-        <v>99.523510360159</v>
-      </c>
-      <c r="C8" s="25">
-        <v>76.3864774117246</v>
+      <c r="B8" s="39">
+        <v>126.017729430459</v>
+      </c>
+      <c r="C8" s="40">
+        <v>106.499148309231</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Februar 2024</t>
         </is>
       </c>
-      <c r="B9" s="24">
-        <v>86.7537441896275</v>
-      </c>
-      <c r="C9" s="25">
-        <v>80.1084393449128</v>
+      <c r="B9" s="39">
+        <v>109.619483784772</v>
+      </c>
+      <c r="C9" s="40">
+        <v>81.9757438777015</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>März 2024</t>
         </is>
       </c>
-      <c r="B10" s="24">
-        <v>108.667711708695</v>
-      </c>
-      <c r="C10" s="25">
-        <v>85.9985851077363</v>
+      <c r="B10" s="39">
+        <v>118.008307782002</v>
+      </c>
+      <c r="C10" s="40">
+        <v>111.852143020369</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Januar 2025</t>
         </is>
       </c>
-      <c r="B11" s="24">
-        <v>116.536815087311</v>
-      </c>
-      <c r="C11" s="25">
-        <v>128.519054492936</v>
+      <c r="B11" s="39">
+        <v>120.255012135021</v>
+      </c>
+      <c r="C11" s="40">
+        <v>91.8242300581187</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Februar 2025</t>
         </is>
       </c>
-      <c r="B12" s="24">
-        <v>101.291730012745</v>
-      </c>
-      <c r="C12" s="25">
-        <v>106.393102286384</v>
+      <c r="B12" s="39">
+        <v>125.475858012214</v>
+      </c>
+      <c r="C12" s="40">
+        <v>99.2152577731758</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>März 2025</t>
         </is>
       </c>
-      <c r="B13" s="24">
-        <v>109.009267557412</v>
-      </c>
-      <c r="C13" s="25">
-        <v>88.7852441053838</v>
+      <c r="B13" s="39">
+        <v>94.0712147112936</v>
+      </c>
+      <c r="C13" s="40">
+        <v>128.341755908914</v>
       </c>
     </row>
   </sheetData>
@@ -1549,151 +1479,160 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>61241-03-b: Tabelle mit 9 Zeilen und 3 Spalten für barrierefreien Zugang.</t>
-        </is>
-      </c>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Tabelle 61241-03. Sie erstreckt sich über 3 Spalten und 9 Zeilen.</t>
+        </is>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Monat_Jahr</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Dieselkraftstoff_ab_Lager</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Dieselkraftstoff_frei_Verbrauchsstelle</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Januar 2023</t>
         </is>
       </c>
-      <c r="B5" s="26">
-        <v>128.245580354705</v>
-      </c>
-      <c r="C5" s="27">
-        <v>113.84433391504</v>
+      <c r="B5" s="43">
+        <v>119.122709678486</v>
+      </c>
+      <c r="C5" s="44">
+        <v>89.2437729332596</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Februar 2023</t>
         </is>
       </c>
-      <c r="B6" s="26">
-        <v>111.428374904208</v>
-      </c>
-      <c r="C6" s="27">
-        <v>93.3277661539614</v>
+      <c r="B6" s="43">
+        <v>100.902110515162</v>
+      </c>
+      <c r="C6" s="44">
+        <v>114.396699322388</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>März 2023</t>
         </is>
       </c>
-      <c r="B7" s="26">
-        <v>128.144519217312</v>
-      </c>
-      <c r="C7" s="27">
-        <v>91.056316816248</v>
+      <c r="B7" s="43">
+        <v>99.4472182774916</v>
+      </c>
+      <c r="C7" s="44">
+        <v>77.5183631898835</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Januar 2024</t>
         </is>
       </c>
-      <c r="B8" s="26">
-        <v>99.523510360159</v>
-      </c>
-      <c r="C8" s="27">
-        <v>76.3864774117246</v>
+      <c r="B8" s="43">
+        <v>126.017729430459</v>
+      </c>
+      <c r="C8" s="44">
+        <v>106.499148309231</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Februar 2024</t>
         </is>
       </c>
-      <c r="B9" s="26">
-        <v>86.7537441896275</v>
-      </c>
-      <c r="C9" s="27">
-        <v>80.1084393449128</v>
+      <c r="B9" s="43">
+        <v>109.619483784772</v>
+      </c>
+      <c r="C9" s="44">
+        <v>81.9757438777015</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>März 2024</t>
         </is>
       </c>
-      <c r="B10" s="26">
-        <v>108.667711708695</v>
-      </c>
-      <c r="C10" s="27">
-        <v>85.9985851077363</v>
+      <c r="B10" s="43">
+        <v>118.008307782002</v>
+      </c>
+      <c r="C10" s="44">
+        <v>111.852143020369</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Januar 2025</t>
         </is>
       </c>
-      <c r="B11" s="26">
-        <v>116.536815087311</v>
-      </c>
-      <c r="C11" s="27">
-        <v>128.519054492936</v>
+      <c r="B11" s="43">
+        <v>120.255012135021</v>
+      </c>
+      <c r="C11" s="44">
+        <v>91.8242300581187</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Februar 2025</t>
         </is>
       </c>
-      <c r="B12" s="26">
-        <v>101.291730012745</v>
-      </c>
-      <c r="C12" s="27">
-        <v>106.393102286384</v>
+      <c r="B12" s="43">
+        <v>125.475858012214</v>
+      </c>
+      <c r="C12" s="44">
+        <v>99.2152577731758</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>März 2025</t>
         </is>
       </c>
-      <c r="B13" s="26">
-        <v>109.009267557412</v>
-      </c>
-      <c r="C13" s="27">
-        <v>88.7852441053838</v>
+      <c r="B13" s="43">
+        <v>94.0712147112936</v>
+      </c>
+      <c r="C13" s="44">
+        <v>128.341755908914</v>
       </c>
     </row>
   </sheetData>
@@ -1708,230 +1647,164 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Monat_Jahr</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Dieselkraftstoff_ab_Lager</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Dieselkraftstoff_frei_Verbrauchsstelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Januar 2023</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>128.245580354705</v>
-      </c>
-      <c r="D2">
-        <v>113.84433391504</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Februar 2023</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>111.428374904208</v>
-      </c>
-      <c r="D3">
-        <v>93.3277661539614</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>März 2023</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>128.144519217312</v>
-      </c>
-      <c r="D4">
-        <v>91.056316816248</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Januar 2024</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>99.523510360159</v>
-      </c>
-      <c r="D5">
-        <v>76.3864774117246</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Februar 2024</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>86.7537441896275</v>
-      </c>
-      <c r="D6">
-        <v>80.1084393449128</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>März 2024</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>108.667711708695</v>
-      </c>
-      <c r="D7">
-        <v>85.9985851077363</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Januar 2025</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>116.536815087311</v>
-      </c>
-      <c r="D8">
-        <v>128.519054492936</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Februar 2025</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>101.291730012745</v>
-      </c>
-      <c r="D9">
-        <v>106.393102286384</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>März 2025</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>109.009267557412</v>
-      </c>
-      <c r="D10">
-        <v>88.7852441053838</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="1" gridLinesSet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Informationen zur Barrierefreiheit</t>
-        </is>
-      </c>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CSV-Daten zu Tabelle 61241-03</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Diese Publikation enthält eine oder mehrere barrierefreie Tabellen, die durch die Tabellenbezeichnung "-b" erkennbar und am Anfang des Tabellenteils zu finden sind.</t>
-        </is>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Monat_Jahr</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Dieselkraftstoff_ab_Lager</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Dieselkraftstoff_frei_Verbrauchsstelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Januar 2023</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <v>119.122709678486</v>
+      </c>
+      <c r="C5" s="8">
+        <v>89.2437729332596</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Februar 2023</t>
+        </is>
+      </c>
+      <c r="B6" s="8">
+        <v>100.902110515162</v>
+      </c>
+      <c r="C6" s="8">
+        <v>114.396699322388</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>März 2023</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <v>99.4472182774916</v>
+      </c>
+      <c r="C7" s="8">
+        <v>77.5183631898835</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Januar 2024</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
+        <v>126.017729430459</v>
+      </c>
+      <c r="C8" s="8">
+        <v>106.499148309231</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Februar 2024</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
+        <v>109.619483784772</v>
+      </c>
+      <c r="C9" s="8">
+        <v>81.9757438777015</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>März 2024</t>
+        </is>
+      </c>
+      <c r="B10" s="8">
+        <v>118.008307782002</v>
+      </c>
+      <c r="C10" s="8">
+        <v>111.852143020369</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Januar 2025</t>
+        </is>
+      </c>
+      <c r="B11" s="8">
+        <v>120.255012135021</v>
+      </c>
+      <c r="C11" s="8">
+        <v>91.8242300581187</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Februar 2025</t>
+        </is>
+      </c>
+      <c r="B12" s="8">
+        <v>125.475858012214</v>
+      </c>
+      <c r="C12" s="8">
+        <v>99.2152577731758</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>März 2025</t>
+        </is>
+      </c>
+      <c r="B13" s="8">
+        <v>94.0712147112936</v>
+      </c>
+      <c r="C13" s="8">
+        <v>128.341755908914</v>
       </c>
     </row>
   </sheetData>
@@ -1944,114 +1817,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-  </cols>
   <sheetData>
-    <row customHeight="1" ht="25" r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Inhaltsübersicht</t>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Informationen zur Barrierefreiheit</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>GENESIS-Online</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Impressum</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Informationen zur Statistik</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Tabellen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>61241-01 - Layout-Tabelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>61241-01 -b - Barrierefreie Tabelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>61241-02 - Layout-Tabelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>61241-02 -b - Barrierefreie Tabelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>61241-03 - Layout-Tabelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>61241-03 -b - Barrierefreie Tabelle</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Dieses Dokument wurde nach den Richtlinien für Barrierefreiheit erstellt.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="A3" r:id="rId2"/>
-    <hyperlink ref="A4" r:id="rId3"/>
-    <hyperlink ref="A5" r:id="rId4"/>
-    <hyperlink ref="A8" r:id="rId5"/>
-    <hyperlink ref="A9" r:id="rId6"/>
-    <hyperlink ref="A10" r:id="rId7"/>
-    <hyperlink ref="A11" r:id="rId8"/>
-    <hyperlink ref="A12" r:id="rId9"/>
-    <hyperlink ref="A13" r:id="rId10"/>
+    <hyperlink ref="A1" r:id="rId1"/>
   </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2059,9 +1853,130 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Inhaltsübersicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Informationen zur Barrierefreiheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Übersicht GENESIS-Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Impressum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Informationen zur Statistik</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Barrierefreie Tabellen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Tabellen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>61241-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>61241-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>61241-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A10" r:id="rId5"/>
+    <hyperlink ref="A11" r:id="rId6"/>
+    <hyperlink ref="A12" r:id="rId7"/>
+  </hyperlinks>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -2071,8 +1986,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>GENESIS-Online</t>
         </is>
@@ -2090,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -2100,8 +2015,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Impressum</t>
         </is>
@@ -2119,7 +2034,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -2129,8 +2044,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Informationen zur Statistik</t>
         </is>
@@ -2150,156 +2065,163 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>61241-01: Preise für ausgewählte Mineralölerzeugnisse</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monat und Jahr</t>
-        </is>
-      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Erzeugnis</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Frachtlage</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Berichtsort</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>EUR_je_hl_JD_2025</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>EUR_je_hl_Dez_2024</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>EUR_je_hl_Nov_2025</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>EUR_je_hl_Dez_2025</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Motorenbenzin E 5</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>ab Lager</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="20">
         <v>133.43</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="21">
         <v>132.73</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="22">
         <v>135</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="23">
         <v>128.89</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Dieselkraftstoff</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>ab Lager</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="20">
         <v>121.45</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="21">
         <v>121.86</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="22">
         <v>125.38</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="23">
         <v>117.83</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Dieselkraftstoff</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>frei Verbrauchsstelle</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="20">
         <v>124.65</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="21">
         <v>125.03</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="22">
         <v>128.78</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="23">
         <v>121.31</v>
       </c>
     </row>
@@ -2319,140 +2241,161 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>61241-01-b: Tabelle mit 3 Zeilen und 7 Spalten für barrierefreien Zugang.</t>
-        </is>
-      </c>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Tabelle 61241-01. Sie erstreckt sich über 7 Spalten und 3 Zeilen.</t>
+        </is>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>zur Inhaltsübersicht</t>
         </is>
       </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Erzeugnis</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Frachtlage</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Berichtsort</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>EUR_je_hl_JD_2025</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>EUR_je_hl_Dez_2024</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>EUR_je_hl_Nov_2025</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>EUR_je_hl_Dez_2025</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Motorenbenzin E 5</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>ab Lager</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="29">
         <v>133.43</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="30">
         <v>132.73</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="31">
         <v>135</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="32">
         <v>128.89</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Dieselkraftstoff</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>ab Lager</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="29">
         <v>121.45</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="30">
         <v>121.86</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="31">
         <v>125.38</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="32">
         <v>117.83</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Dieselkraftstoff</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>frei Verbrauchsstelle</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="29">
         <v>124.65</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="30">
         <v>125.03</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="31">
         <v>128.78</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="32">
         <v>121.31</v>
       </c>
     </row>
@@ -2468,162 +2411,172 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CSV-Daten zu Tabelle 61241-01</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>zur Inhaltsübersicht</t>
+        </is>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Erzeugnis</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Frachtlage</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Berichtsort</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>EUR_je_hl_JD_2025</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>EUR_je_hl_Dez_2024</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>EUR_je_hl_Nov_2025</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>EUR_je_hl_Dez_2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Motorenbenzin E 5</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>ab Lager</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="D5" s="8">
         <v>133.43</v>
       </c>
-      <c r="F2">
+      <c r="E5" s="8">
         <v>132.73</v>
       </c>
-      <c r="G2">
+      <c r="F5" s="8">
         <v>135</v>
       </c>
-      <c r="H2">
+      <c r="G5" s="8">
         <v>128.89</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Dieselkraftstoff</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>ab Lager</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="D6" s="8">
         <v>121.45</v>
       </c>
-      <c r="F3">
+      <c r="E6" s="8">
         <v>121.86</v>
       </c>
-      <c r="G3">
+      <c r="F6" s="8">
         <v>125.38</v>
       </c>
-      <c r="H3">
+      <c r="G6" s="8">
         <v>117.83</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Erzeugerpreise gewerblicher Produkte</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Dieselkraftstoff</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>frei Verbrauchsstelle</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="D7" s="8">
         <v>124.65</v>
       </c>
-      <c r="F4">
+      <c r="E7" s="8">
         <v>125.03</v>
       </c>
-      <c r="G4">
+      <c r="F7" s="8">
         <v>128.78</v>
       </c>
-      <c r="H4">
+      <c r="G7" s="8">
         <v>121.31</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/projects/skill_modify_excel_with_r/statistischer_bericht_demo.xlsx
+++ b/projects/skill_modify_excel_with_r/statistischer_bericht_demo.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <v>135.865793242119</v>
+        <v>105.905799367465</v>
       </c>
     </row>
     <row r="6">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B6" s="34">
-        <v>138.344800015911</v>
+        <v>131.966114146635</v>
       </c>
     </row>
     <row r="7">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B7" s="34">
-        <v>133.20068910718</v>
+        <v>95.3186941938475</v>
       </c>
     </row>
     <row r="8">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B8" s="34">
-        <v>135.121662043966</v>
+        <v>128.357382211834</v>
       </c>
     </row>
     <row r="9">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B9" s="34">
-        <v>89.1757570626214</v>
+        <v>116.974370111711</v>
       </c>
     </row>
     <row r="10">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B10" s="34">
-        <v>126.497217006981</v>
+        <v>94.5007804967463</v>
       </c>
     </row>
     <row r="11">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B11" s="34">
-        <v>102.724851034582</v>
+        <v>125.931678824127</v>
       </c>
     </row>
     <row r="12">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B12" s="34">
-        <v>98.9447790849954</v>
+        <v>89.2110710265115</v>
       </c>
     </row>
     <row r="13">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B13" s="34">
-        <v>113.418734893203</v>
+        <v>86.9931826507673</v>
       </c>
     </row>
     <row r="14">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B14" s="34">
-        <v>124.949937295169</v>
+        <v>132.91046529077</v>
       </c>
     </row>
     <row r="15">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B15" s="34">
-        <v>103.58089662157</v>
+        <v>96.1148510407656</v>
       </c>
     </row>
     <row r="16">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B16" s="34">
-        <v>134.48971261736</v>
+        <v>116.35068112053</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B17" s="34">
-        <v>123.35365481209</v>
+        <v>88.4663458447903</v>
       </c>
     </row>
     <row r="18">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B18" s="34">
-        <v>91.7267335392535</v>
+        <v>100.872728489339</v>
       </c>
     </row>
     <row r="19">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B19" s="34">
-        <v>135.919500230812</v>
+        <v>118.870501392521</v>
       </c>
     </row>
     <row r="20">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="B20" s="34">
-        <v>103.738525854424</v>
+        <v>103.100048601627</v>
       </c>
     </row>
     <row r="21">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="B21" s="34">
-        <v>83.6907474184409</v>
+        <v>139.70547048375</v>
       </c>
     </row>
     <row r="22">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="B22" s="34">
-        <v>85.6497246865183</v>
+        <v>97.4758795974776</v>
       </c>
     </row>
     <row r="23">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B23" s="34">
-        <v>99.7990381531417</v>
+        <v>135.952352848835</v>
       </c>
     </row>
     <row r="24">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B24" s="34">
-        <v>136.984818275087</v>
+        <v>96.9721685536206</v>
       </c>
     </row>
   </sheetData>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="36">
-        <v>135.865793242119</v>
+        <v>105.905799367465</v>
       </c>
     </row>
     <row r="6">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B6" s="36">
-        <v>138.344800015911</v>
+        <v>131.966114146635</v>
       </c>
     </row>
     <row r="7">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B7" s="36">
-        <v>133.20068910718</v>
+        <v>95.3186941938475</v>
       </c>
     </row>
     <row r="8">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B8" s="36">
-        <v>135.121662043966</v>
+        <v>128.357382211834</v>
       </c>
     </row>
     <row r="9">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B9" s="36">
-        <v>89.1757570626214</v>
+        <v>116.974370111711</v>
       </c>
     </row>
     <row r="10">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B10" s="36">
-        <v>126.497217006981</v>
+        <v>94.5007804967463</v>
       </c>
     </row>
     <row r="11">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B11" s="36">
-        <v>102.724851034582</v>
+        <v>125.931678824127</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B12" s="36">
-        <v>98.9447790849954</v>
+        <v>89.2110710265115</v>
       </c>
     </row>
     <row r="13">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B13" s="36">
-        <v>113.418734893203</v>
+        <v>86.9931826507673</v>
       </c>
     </row>
     <row r="14">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B14" s="36">
-        <v>124.949937295169</v>
+        <v>132.91046529077</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="B15" s="36">
-        <v>103.58089662157</v>
+        <v>96.1148510407656</v>
       </c>
     </row>
     <row r="16">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B16" s="36">
-        <v>134.48971261736</v>
+        <v>116.35068112053</v>
       </c>
     </row>
     <row r="17">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B17" s="36">
-        <v>123.35365481209</v>
+        <v>88.4663458447903</v>
       </c>
     </row>
     <row r="18">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B18" s="36">
-        <v>91.7267335392535</v>
+        <v>100.872728489339</v>
       </c>
     </row>
     <row r="19">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B19" s="36">
-        <v>135.919500230812</v>
+        <v>118.870501392521</v>
       </c>
     </row>
     <row r="20">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="B20" s="36">
-        <v>103.738525854424</v>
+        <v>103.100048601627</v>
       </c>
     </row>
     <row r="21">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B21" s="36">
-        <v>83.6907474184409</v>
+        <v>139.70547048375</v>
       </c>
     </row>
     <row r="22">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="B22" s="36">
-        <v>85.6497246865183</v>
+        <v>97.4758795974776</v>
       </c>
     </row>
     <row r="23">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B23" s="36">
-        <v>99.7990381531417</v>
+        <v>135.952352848835</v>
       </c>
     </row>
     <row r="24">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B24" s="36">
-        <v>136.984818275087</v>
+        <v>96.9721685536206</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <v>135.865793242119</v>
+        <v>105.905799367465</v>
       </c>
     </row>
     <row r="6">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>138.344800015911</v>
+        <v>131.966114146635</v>
       </c>
     </row>
     <row r="7">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>133.20068910718</v>
+        <v>95.3186941938475</v>
       </c>
     </row>
     <row r="8">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>135.121662043966</v>
+        <v>128.357382211834</v>
       </c>
     </row>
     <row r="9">
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <v>89.1757570626214</v>
+        <v>116.974370111711</v>
       </c>
     </row>
     <row r="10">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <v>126.497217006981</v>
+        <v>94.5007804967463</v>
       </c>
     </row>
     <row r="11">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <v>102.724851034582</v>
+        <v>125.931678824127</v>
       </c>
     </row>
     <row r="12">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>98.9447790849954</v>
+        <v>89.2110710265115</v>
       </c>
     </row>
     <row r="13">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <v>113.418734893203</v>
+        <v>86.9931826507673</v>
       </c>
     </row>
     <row r="14">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <v>124.949937295169</v>
+        <v>132.91046529077</v>
       </c>
     </row>
     <row r="15">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <v>103.58089662157</v>
+        <v>96.1148510407656</v>
       </c>
     </row>
     <row r="16">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <v>134.48971261736</v>
+        <v>116.35068112053</v>
       </c>
     </row>
     <row r="17">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <v>123.35365481209</v>
+        <v>88.4663458447903</v>
       </c>
     </row>
     <row r="18">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <v>91.7267335392535</v>
+        <v>100.872728489339</v>
       </c>
     </row>
     <row r="19">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <v>135.919500230812</v>
+        <v>118.870501392521</v>
       </c>
     </row>
     <row r="20">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <v>103.738525854424</v>
+        <v>103.100048601627</v>
       </c>
     </row>
     <row r="21">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <v>83.6907474184409</v>
+        <v>139.70547048375</v>
       </c>
     </row>
     <row r="22">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <v>85.6497246865183</v>
+        <v>97.4758795974776</v>
       </c>
     </row>
     <row r="23">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <v>99.7990381531417</v>
+        <v>135.952352848835</v>
       </c>
     </row>
     <row r="24">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <v>136.984818275087</v>
+        <v>96.9721685536206</v>
       </c>
     </row>
   </sheetData>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B5" s="39">
-        <v>119.122709678486</v>
+        <v>119.442247231491</v>
       </c>
       <c r="C5" s="40">
-        <v>89.2437729332596</v>
+        <v>83.9680439466611</v>
       </c>
     </row>
     <row r="6">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B6" s="39">
-        <v>100.902110515162</v>
+        <v>88.1145895877853</v>
       </c>
       <c r="C6" s="40">
-        <v>114.396699322388</v>
+        <v>96.1981655471027</v>
       </c>
     </row>
     <row r="7">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B7" s="39">
-        <v>99.4472182774916</v>
+        <v>101.819765870459</v>
       </c>
       <c r="C7" s="40">
-        <v>77.5183631898835</v>
+        <v>109.109313902445</v>
       </c>
     </row>
     <row r="8">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B8" s="39">
-        <v>126.017729430459</v>
+        <v>101.067681852728</v>
       </c>
       <c r="C8" s="40">
-        <v>106.499148309231</v>
+        <v>75.3167336247861</v>
       </c>
     </row>
     <row r="9">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B9" s="39">
-        <v>109.619483784772</v>
+        <v>109.065047558397</v>
       </c>
       <c r="C9" s="40">
-        <v>81.9757438777015</v>
+        <v>110.141521235928</v>
       </c>
     </row>
     <row r="10">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B10" s="39">
-        <v>118.008307782002</v>
+        <v>99.2210973287001</v>
       </c>
       <c r="C10" s="40">
-        <v>111.852143020369</v>
+        <v>103.916423069313</v>
       </c>
     </row>
     <row r="11">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B11" s="39">
-        <v>120.255012135021</v>
+        <v>126.015758216381</v>
       </c>
       <c r="C11" s="40">
-        <v>91.8242300581187</v>
+        <v>99.5408828789368</v>
       </c>
     </row>
     <row r="12">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B12" s="39">
-        <v>125.475858012214</v>
+        <v>85.4217962827533</v>
       </c>
       <c r="C12" s="40">
-        <v>99.2152577731758</v>
+        <v>97.8942067036405</v>
       </c>
     </row>
     <row r="13">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B13" s="39">
-        <v>94.0712147112936</v>
+        <v>112.623494961299</v>
       </c>
       <c r="C13" s="40">
-        <v>128.341755908914</v>
+        <v>129.170396779664</v>
       </c>
     </row>
   </sheetData>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="B5" s="43">
-        <v>119.122709678486</v>
+        <v>119.442247231491</v>
       </c>
       <c r="C5" s="44">
-        <v>89.2437729332596</v>
+        <v>83.9680439466611</v>
       </c>
     </row>
     <row r="6">
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="B6" s="43">
-        <v>100.902110515162</v>
+        <v>88.1145895877853</v>
       </c>
       <c r="C6" s="44">
-        <v>114.396699322388</v>
+        <v>96.1981655471027</v>
       </c>
     </row>
     <row r="7">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="B7" s="43">
-        <v>99.4472182774916</v>
+        <v>101.819765870459</v>
       </c>
       <c r="C7" s="44">
-        <v>77.5183631898835</v>
+        <v>109.109313902445</v>
       </c>
     </row>
     <row r="8">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="B8" s="43">
-        <v>126.017729430459</v>
+        <v>101.067681852728</v>
       </c>
       <c r="C8" s="44">
-        <v>106.499148309231</v>
+        <v>75.3167336247861</v>
       </c>
     </row>
     <row r="9">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="B9" s="43">
-        <v>109.619483784772</v>
+        <v>109.065047558397</v>
       </c>
       <c r="C9" s="44">
-        <v>81.9757438777015</v>
+        <v>110.141521235928</v>
       </c>
     </row>
     <row r="10">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="B10" s="43">
-        <v>118.008307782002</v>
+        <v>99.2210973287001</v>
       </c>
       <c r="C10" s="44">
-        <v>111.852143020369</v>
+        <v>103.916423069313</v>
       </c>
     </row>
     <row r="11">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="B11" s="43">
-        <v>120.255012135021</v>
+        <v>126.015758216381</v>
       </c>
       <c r="C11" s="44">
-        <v>91.8242300581187</v>
+        <v>99.5408828789368</v>
       </c>
     </row>
     <row r="12">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="B12" s="43">
-        <v>125.475858012214</v>
+        <v>85.4217962827533</v>
       </c>
       <c r="C12" s="44">
-        <v>99.2152577731758</v>
+        <v>97.8942067036405</v>
       </c>
     </row>
     <row r="13">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="B13" s="43">
-        <v>94.0712147112936</v>
+        <v>112.623494961299</v>
       </c>
       <c r="C13" s="44">
-        <v>128.341755908914</v>
+        <v>129.170396779664</v>
       </c>
     </row>
   </sheetData>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <v>119.122709678486</v>
+        <v>119.442247231491</v>
       </c>
       <c r="C5" s="8">
-        <v>89.2437729332596</v>
+        <v>83.9680439466611</v>
       </c>
     </row>
     <row r="6">
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>100.902110515162</v>
+        <v>88.1145895877853</v>
       </c>
       <c r="C6" s="8">
-        <v>114.396699322388</v>
+        <v>96.1981655471027</v>
       </c>
     </row>
     <row r="7">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>99.4472182774916</v>
+        <v>101.819765870459</v>
       </c>
       <c r="C7" s="8">
-        <v>77.5183631898835</v>
+        <v>109.109313902445</v>
       </c>
     </row>
     <row r="8">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>126.017729430459</v>
+        <v>101.067681852728</v>
       </c>
       <c r="C8" s="8">
-        <v>106.499148309231</v>
+        <v>75.3167336247861</v>
       </c>
     </row>
     <row r="9">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <v>109.619483784772</v>
+        <v>109.065047558397</v>
       </c>
       <c r="C9" s="8">
-        <v>81.9757438777015</v>
+        <v>110.141521235928</v>
       </c>
     </row>
     <row r="10">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <v>118.008307782002</v>
+        <v>99.2210973287001</v>
       </c>
       <c r="C10" s="8">
-        <v>111.852143020369</v>
+        <v>103.916423069313</v>
       </c>
     </row>
     <row r="11">
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <v>120.255012135021</v>
+        <v>126.015758216381</v>
       </c>
       <c r="C11" s="8">
-        <v>91.8242300581187</v>
+        <v>99.5408828789368</v>
       </c>
     </row>
     <row r="12">
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>125.475858012214</v>
+        <v>85.4217962827533</v>
       </c>
       <c r="C12" s="8">
-        <v>99.2152577731758</v>
+        <v>97.8942067036405</v>
       </c>
     </row>
     <row r="13">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <v>94.0712147112936</v>
+        <v>112.623494961299</v>
       </c>
       <c r="C13" s="8">
-        <v>128.341755908914</v>
+        <v>129.170396779664</v>
       </c>
     </row>
   </sheetData>
